--- a/placares-editaveis.xlsx
+++ b/placares-editaveis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="R1a162c694e064f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Editar placares" sheetId="2" r:id="Rce2fb7e051034c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Times" sheetId="3" r:id="R62b4157522714d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="Rb516d8aacf2d47d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Editar placares" sheetId="2" r:id="R8c54b71cfa0b4ead"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Times" sheetId="3" r:id="R93bc21e2c25b4333"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -662,9 +662,7 @@
       <x:c r="D4" s="21" t="str">
         <x:v>2026-04-30</x:v>
       </x:c>
-      <x:c r="E4" s="21" t="str">
-        <x:v>2026-06-07</x:v>
-      </x:c>
+      <x:c r="E4" s="21" t="str"/>
       <x:c r="F4" s="15" t="str">
         <x:v>20:30</x:v>
       </x:c>
@@ -672,20 +670,18 @@
         <x:v>Florida Gators</x:v>
       </x:c>
       <x:c r="H4" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I4" s="15" t="str">
         <x:v>Houston Cougars</x:v>
       </x:c>
       <x:c r="J4" s="15" t="n">
-        <x:v>40</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K4" s="15" t="str">
         <x:v>Final</x:v>
       </x:c>
-      <x:c r="L4" s="16" t="str">
-        <x:v>Jogo remarcado no box score</x:v>
-      </x:c>
+      <x:c r="L4" s="16" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -775,13 +771,17 @@
       <x:c r="G7" s="15" t="str">
         <x:v>Michigan Wolverines</x:v>
       </x:c>
-      <x:c r="H7" s="15" t="str"/>
+      <x:c r="H7" s="15" t="n">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="I7" s="15" t="str">
         <x:v>Houston Cougars</x:v>
       </x:c>
-      <x:c r="J7" s="15" t="str"/>
+      <x:c r="J7" s="15" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="K7" s="15" t="str">
-        <x:v>Agendado</x:v>
+        <x:v>Final</x:v>
       </x:c>
       <x:c r="L7" s="16" t="str"/>
     </x:row>
@@ -972,30 +972,22 @@
       <x:c r="D13" s="21" t="str">
         <x:v>2026-05-19</x:v>
       </x:c>
-      <x:c r="E13" s="21" t="str">
-        <x:v>2026-05-24</x:v>
-      </x:c>
+      <x:c r="E13" s="21" t="str"/>
       <x:c r="F13" s="15" t="str">
         <x:v>22:00</x:v>
       </x:c>
       <x:c r="G13" s="15" t="str">
         <x:v>North Carolina Tar Heels</x:v>
       </x:c>
-      <x:c r="H13" s="15" t="n">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="H13" s="15" t="str"/>
       <x:c r="I13" s="15" t="str">
         <x:v>Florida Gators</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>66</x:v>
-      </x:c>
+      <x:c r="J13" s="15" t="str"/>
       <x:c r="K13" s="15" t="str">
-        <x:v>Final</x:v>
-      </x:c>
-      <x:c r="L13" s="16" t="str">
-        <x:v>Jogo remarcado no box score</x:v>
-      </x:c>
+        <x:v>Agendado</x:v>
+      </x:c>
+      <x:c r="L13" s="16" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
@@ -1321,7 +1313,7 @@
         <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="E23" s="21" t="str">
-        <x:v>2026-04-30</x:v>
+        <x:v>2026-06-07</x:v>
       </x:c>
       <x:c r="F23" s="15" t="str">
         <x:v>10:30</x:v>
@@ -1330,13 +1322,13 @@
         <x:v>Florida Gators</x:v>
       </x:c>
       <x:c r="H23" s="15" t="n">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
         <x:v>Houston Cougars</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K23" s="15" t="str">
         <x:v>Final</x:v>
@@ -1365,13 +1357,17 @@
       <x:c r="G24" s="15" t="str">
         <x:v>Duke Blue Devils</x:v>
       </x:c>
-      <x:c r="H24" s="15" t="str"/>
+      <x:c r="H24" s="15" t="n">
+        <x:v>68</x:v>
+      </x:c>
       <x:c r="I24" s="15" t="str">
         <x:v>UCLA Bruins</x:v>
       </x:c>
-      <x:c r="J24" s="15" t="str"/>
+      <x:c r="J24" s="15" t="n">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="K24" s="15" t="str">
-        <x:v>Agendado</x:v>
+        <x:v>Final</x:v>
       </x:c>
       <x:c r="L24" s="16" t="str"/>
     </x:row>
@@ -1429,13 +1425,17 @@
       <x:c r="G26" s="15" t="str">
         <x:v>Houston Cougars</x:v>
       </x:c>
-      <x:c r="H26" s="15" t="str"/>
+      <x:c r="H26" s="15" t="n">
+        <x:v>75</x:v>
+      </x:c>
       <x:c r="I26" s="15" t="str">
         <x:v>North Carolina Tar Heels</x:v>
       </x:c>
-      <x:c r="J26" s="15" t="str"/>
+      <x:c r="J26" s="15" t="n">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="K26" s="15" t="str">
-        <x:v>Agendado</x:v>
+        <x:v>Final</x:v>
       </x:c>
       <x:c r="L26" s="16" t="str"/>
     </x:row>
@@ -1459,13 +1459,17 @@
       <x:c r="G27" s="15" t="str">
         <x:v>Indiana Hoosiers</x:v>
       </x:c>
-      <x:c r="H27" s="15" t="str"/>
+      <x:c r="H27" s="15" t="n">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="I27" s="15" t="str">
         <x:v>Michigan Wolverines</x:v>
       </x:c>
-      <x:c r="J27" s="15" t="str"/>
+      <x:c r="J27" s="15" t="n">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="K27" s="15" t="str">
-        <x:v>Agendado</x:v>
+        <x:v>Final</x:v>
       </x:c>
       <x:c r="L27" s="16" t="str"/>
     </x:row>
@@ -1692,22 +1696,30 @@
       <x:c r="D35" s="21" t="str">
         <x:v>2026-07-19</x:v>
       </x:c>
-      <x:c r="E35" s="21" t="str"/>
+      <x:c r="E35" s="21" t="str">
+        <x:v>2026-05-24</x:v>
+      </x:c>
       <x:c r="F35" s="15" t="str">
         <x:v>10:30</x:v>
       </x:c>
       <x:c r="G35" s="15" t="str">
         <x:v>Florida Gators</x:v>
       </x:c>
-      <x:c r="H35" s="15" t="str"/>
+      <x:c r="H35" s="15" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="I35" s="15" t="str">
         <x:v>North Carolina Tar Heels</x:v>
       </x:c>
-      <x:c r="J35" s="15" t="str"/>
+      <x:c r="J35" s="15" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="K35" s="15" t="str">
-        <x:v>Agendado</x:v>
-      </x:c>
-      <x:c r="L35" s="16" t="str"/>
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="L35" s="16" t="str">
+        <x:v>Jogo remarcado no box score</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="14" t="str">
@@ -1913,7 +1925,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R774587f2f3244fd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc60e48d265a4038"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2029,7 +2041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a8fd68c43b4947"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42274f6934b045d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>